--- a/data/trans_camb/IP16A98-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP16A98-Edad-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-14,45; 15,62</t>
+          <t>-13,03; 15,74</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,28; 30,33</t>
+          <t>-7,37; 30,9</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-10,55; 18,28</t>
+          <t>-10,44; 17,74</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-10,98; 14,79</t>
+          <t>-11,23; 16,1</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-7,84; 13,74</t>
+          <t>-7,78; 13,76</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-5,97; 15,65</t>
+          <t>-6,89; 16,34</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-67,79; 178,21</t>
+          <t>-66,37; 191,83</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-45,97; 326,17</t>
+          <t>-45,4; 313,25</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-71,48; 372,78</t>
+          <t>-67,77; 368,35</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-68,92; 271,99</t>
+          <t>-69,75; 314,68</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-48,69; 156,31</t>
+          <t>-45,87; 166,64</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-37,17; 191,62</t>
+          <t>-43,74; 180,3</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,38; 21,9</t>
+          <t>-2,7; 21,98</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,89; 16,02</t>
+          <t>-5,75; 16,58</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,35; 17,23</t>
+          <t>-6,49; 17,58</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,22; 18,83</t>
+          <t>-5,09; 19,83</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 15,22</t>
+          <t>-1,25; 15,43</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 15,02</t>
+          <t>-2,87; 14,03</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-31,79; 376,04</t>
+          <t>-23,12; 395,01</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-45,43; 285,76</t>
+          <t>-44,56; 273,51</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-40,58; 228,03</t>
+          <t>-41,49; 219,37</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-38,82; 225,47</t>
+          <t>-33,16; 232,83</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-10,92; 192,91</t>
+          <t>-14,39; 175,81</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-19,42; 180,96</t>
+          <t>-22,45; 167,45</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-15,67; 14,11</t>
+          <t>-16,78; 14,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-9,7; 22,84</t>
+          <t>-8,33; 23,15</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-12,96; 22,01</t>
+          <t>-12,87; 23,18</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-22,67; 8,1</t>
+          <t>-24,78; 7,23</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-8,88; 14,18</t>
+          <t>-9,54; 12,99</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-11,61; 10,59</t>
+          <t>-12,47; 10,41</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-66,77; 187,63</t>
+          <t>-69,62; 177,27</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-42,41; 265,46</t>
+          <t>-38,63; 317,58</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-48,37; 200,13</t>
+          <t>-44,43; 239,13</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-77,7; 99,39</t>
+          <t>-78,99; 84,16</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-37,9; 131,99</t>
+          <t>-41,8; 117,39</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-48,95; 94,41</t>
+          <t>-48,95; 88,15</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,15; 26,54</t>
+          <t>-2,59; 28,02</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-7,47; 30,23</t>
+          <t>-5,51; 32,56</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-16,6; 23,5</t>
+          <t>-15,58; 22,23</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-15,73; 22,11</t>
+          <t>-16,35; 19,85</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-5,07; 20,52</t>
+          <t>-5,27; 19,89</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-6,46; 20,72</t>
+          <t>-7,42; 19,31</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-56,98; 1164,85</t>
+          <t>-49,3; 1283,8</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-61,21; 1311,3</t>
+          <t>-58,37; 1505,99</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-55,3; 194,42</t>
+          <t>-55,59; 193,97</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-52,2; 202,57</t>
+          <t>-55,01; 164,64</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-28,94; 254,46</t>
+          <t>-31,28; 233,28</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-37,45; 209,5</t>
+          <t>-40,86; 214,81</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 11,83</t>
+          <t>-0,93; 12,88</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,29; 15,75</t>
+          <t>-2,44; 16,88</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 13,49</t>
+          <t>-2,54; 12,61</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-4,01; 11,53</t>
+          <t>-4,58; 10,36</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 10,12</t>
+          <t>-0,1; 10,03</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 10,9</t>
+          <t>-1,95; 10,57</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-13,87; 132,68</t>
+          <t>-7,41; 143,36</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-23,4; 167,95</t>
+          <t>-18,97; 175,55</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-14,01; 121,69</t>
+          <t>-14,46; 109,24</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-24,07; 99,37</t>
+          <t>-24,46; 87,97</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>1,52; 87,15</t>
+          <t>-0,24; 89,39</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-6,23; 92,75</t>
+          <t>-10,18; 87,63</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16A98-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP16A98-Edad-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-13,03; 15,74</t>
+          <t>-13,72; 15,2</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,37; 30,9</t>
+          <t>-8,55; 31,42</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-10,44; 17,74</t>
+          <t>-11,56; 17,62</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-11,23; 16,1</t>
+          <t>-12,34; 14,54</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-7,78; 13,76</t>
+          <t>-8,42; 11,86</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-6,89; 16,34</t>
+          <t>-6,14; 16,74</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-66,37; 191,83</t>
+          <t>-65,03; 204,32</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-45,4; 313,25</t>
+          <t>-43,51; 356,62</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-67,77; 368,35</t>
+          <t>-76,48; 349,38</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-69,75; 314,68</t>
+          <t>-74,97; 284,77</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-45,87; 166,64</t>
+          <t>-47,82; 140,02</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-43,74; 180,3</t>
+          <t>-38,27; 197,24</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,7; 21,98</t>
+          <t>-2,55; 21,14</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,75; 16,58</t>
+          <t>-6,02; 15,85</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,49; 17,58</t>
+          <t>-6,61; 17,4</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,09; 19,83</t>
+          <t>-4,08; 19,58</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 15,43</t>
+          <t>-1,72; 15,09</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,87; 14,03</t>
+          <t>-2,14; 14,15</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-23,12; 395,01</t>
+          <t>-28,16; 406,48</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-44,56; 273,51</t>
+          <t>-47,71; 289,04</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-41,49; 219,37</t>
+          <t>-42,68; 196,89</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-33,16; 232,83</t>
+          <t>-26,71; 264,2</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-14,39; 175,81</t>
+          <t>-16,3; 175,34</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-22,45; 167,45</t>
+          <t>-18,19; 167,88</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-16,78; 14,0</t>
+          <t>-16,07; 14,1</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-8,33; 23,15</t>
+          <t>-9,45; 23,46</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-12,87; 23,18</t>
+          <t>-13,67; 23,83</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-24,78; 7,23</t>
+          <t>-24,14; 8,85</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-9,54; 12,99</t>
+          <t>-9,61; 13,92</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-12,47; 10,41</t>
+          <t>-12,82; 9,38</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-69,62; 177,27</t>
+          <t>-68,8; 207,58</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-38,63; 317,58</t>
+          <t>-43,13; 263,29</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-44,43; 239,13</t>
+          <t>-47,08; 247,4</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-78,99; 84,16</t>
+          <t>-77,33; 112,71</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-41,8; 117,39</t>
+          <t>-41,91; 124,94</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-48,95; 88,15</t>
+          <t>-51,09; 81,22</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 28,02</t>
+          <t>-3,12; 26,82</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-5,51; 32,56</t>
+          <t>-5,64; 32,99</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-15,58; 22,23</t>
+          <t>-17,55; 22,78</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-16,35; 19,85</t>
+          <t>-15,87; 20,49</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-5,27; 19,89</t>
+          <t>-5,62; 19,24</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-7,42; 19,31</t>
+          <t>-8,86; 19,82</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-49,3; 1283,8</t>
+          <t>-46,99; —</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-58,37; 1505,99</t>
+          <t>-51,75; —</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-55,59; 193,97</t>
+          <t>-56,4; 180,64</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-55,01; 164,64</t>
+          <t>-53,51; 175,57</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-31,28; 233,28</t>
+          <t>-33,97; 198,93</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-40,86; 214,81</t>
+          <t>-43,34; 213,37</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 12,88</t>
+          <t>-1,63; 12,02</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,44; 16,88</t>
+          <t>-2,55; 15,77</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-2,54; 12,61</t>
+          <t>-2,05; 13,37</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-4,58; 10,36</t>
+          <t>-3,81; 11,73</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,1; 10,03</t>
+          <t>-0,4; 10,16</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 10,57</t>
+          <t>-1,22; 10,97</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-7,41; 143,36</t>
+          <t>-11,62; 132,4</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-18,97; 175,55</t>
+          <t>-19,55; 155,84</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-14,46; 109,24</t>
+          <t>-12,69; 108,96</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-24,46; 87,97</t>
+          <t>-20,72; 102,43</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 89,39</t>
+          <t>-3,15; 86,3</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-10,18; 87,63</t>
+          <t>-7,33; 97,83</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16A98-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP16A98-Edad-trans_camb.xlsx
@@ -513,19 +513,19 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han  consumido otros medicamentos</t>
+          <t>Menores que consumieron otros medicamentos</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -593,22 +593,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2,46</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3,18</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>0,78</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>9,06</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2,46</t>
-        </is>
-      </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,81</t>
+          <t>9,08</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,57</t>
+          <t>5,68</t>
         </is>
       </c>
     </row>
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-13,72; 15,2</t>
+          <t>-10,55; 18,28</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,55; 31,42</t>
+          <t>-9,78; 17,34</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-11,56; 17,62</t>
+          <t>-14,45; 15,62</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-12,34; 14,54</t>
+          <t>-8,3; 30,96</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-8,42; 11,86</t>
+          <t>-7,84; 13,74</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-6,14; 16,74</t>
+          <t>-5,54; 16,97</t>
         </is>
       </c>
     </row>
@@ -669,22 +669,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>21,63%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>27,97%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>5,11%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>59,49%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>21,63%</t>
-        </is>
-      </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>59,62%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>34,44%</t>
+          <t>42,87%</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-65,03; 204,32</t>
+          <t>-71,48; 372,78</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-43,51; 356,62</t>
+          <t>-69,07; 295,35</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-76,48; 349,38</t>
+          <t>-67,79; 178,21</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-74,97; 284,77</t>
+          <t>-46,34; 330,21</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-47,82; 140,02</t>
+          <t>-48,69; 156,31</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-38,27; 197,24</t>
+          <t>-34,32; 205,07</t>
         </is>
       </c>
     </row>
@@ -749,22 +749,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>4,87</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>5,42</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>8,55</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>4,54</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>4,87</t>
-        </is>
-      </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6,04</t>
+          <t>7,17</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>5,19</t>
+          <t>6,14</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,55; 21,14</t>
+          <t>-6,35; 17,23</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,02; 15,85</t>
+          <t>-6,54; 17,84</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,61; 17,4</t>
+          <t>-3,38; 21,9</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,08; 19,58</t>
+          <t>-3,48; 19,7</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,72; 15,09</t>
+          <t>-1,51; 15,22</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 14,15</t>
+          <t>-1,95; 15,87</t>
         </is>
       </c>
     </row>
@@ -825,22 +825,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>37,9%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>42,14%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>85,7%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>45,45%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>37,9%</t>
-        </is>
-      </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>47,01%</t>
+          <t>71,8%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>44,91%</t>
+          <t>53,12%</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-28,16; 406,48</t>
+          <t>-40,58; 228,03</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-47,71; 289,04</t>
+          <t>-40,95; 213,18</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-42,68; 196,89</t>
+          <t>-31,79; 376,04</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-26,71; 264,2</t>
+          <t>-31,09; 379,95</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-16,3; 175,34</t>
+          <t>-10,92; 192,91</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-18,19; 167,88</t>
+          <t>-14,68; 190,33</t>
         </is>
       </c>
     </row>
@@ -905,22 +905,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>5,48</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-7,39</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>-0,86</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>6,76</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>5,48</t>
-        </is>
-      </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-7,12</t>
+          <t>6,61</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-0,64</t>
+          <t>-0,68</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-16,07; 14,1</t>
+          <t>-12,96; 22,01</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-9,45; 23,46</t>
+          <t>-23,06; 7,55</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-13,67; 23,83</t>
+          <t>-15,67; 14,11</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-24,14; 8,85</t>
+          <t>-9,78; 22,17</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-9,61; 13,92</t>
+          <t>-8,88; 14,18</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-12,82; 9,38</t>
+          <t>-11,66; 10,52</t>
         </is>
       </c>
     </row>
@@ -981,22 +981,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>27,4%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-36,94%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>-5,24%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>41,42%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>27,4%</t>
-        </is>
-      </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-35,6%</t>
+          <t>40,5%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-3,56%</t>
+          <t>-3,76%</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-68,8; 207,58</t>
+          <t>-48,37; 200,13</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-43,13; 263,29</t>
+          <t>-78,68; 102,31</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-47,08; 247,4</t>
+          <t>-66,77; 187,63</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-77,33; 112,71</t>
+          <t>-41,87; 260,51</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-41,91; 124,94</t>
+          <t>-37,9; 131,99</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-51,09; 81,22</t>
+          <t>-49,43; 95,49</t>
         </is>
       </c>
     </row>
@@ -1061,22 +1061,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>2,42</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>1,52</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>10,63</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>10,18</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>2,42</t>
-        </is>
-      </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1,72</t>
+          <t>10,16</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,9</t>
+          <t>6,43</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,12; 26,82</t>
+          <t>-16,6; 23,5</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-5,64; 32,99</t>
+          <t>-15,58; 22,57</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-17,55; 22,78</t>
+          <t>-4,15; 26,54</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-15,87; 20,49</t>
+          <t>-2,28; 20,85</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-5,62; 19,24</t>
+          <t>-5,07; 20,52</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-8,86; 19,82</t>
+          <t>-4,23; 18,49</t>
         </is>
       </c>
     </row>
@@ -1137,22 +1137,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>11,01%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>6,92%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>148,64%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>142,37%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>11,01%</t>
-        </is>
-      </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>142,02%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>41,15%</t>
+          <t>44,83%</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-46,99; —</t>
+          <t>-55,3; 194,42</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-51,75; —</t>
+          <t>-53,7; 209,54</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-56,4; 180,64</t>
+          <t>-56,98; 1164,85</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-53,51; 175,57</t>
+          <t>-40,19; 875,81</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-33,97; 198,93</t>
+          <t>-28,94; 254,46</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-43,34; 213,37</t>
+          <t>-24,98; 195,23</t>
         </is>
       </c>
     </row>
@@ -1217,22 +1217,22 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>5,13</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>3,18</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
           <t>4,92</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>6,34</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>5,13</t>
-        </is>
-      </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3,21</t>
+          <t>7,37</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,72</t>
+          <t>5,18</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 12,02</t>
+          <t>-2,63; 13,49</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,55; 15,77</t>
+          <t>-4,24; 12,08</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 13,37</t>
+          <t>-1,99; 11,83</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,81; 11,73</t>
+          <t>0,18; 14,64</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 10,16</t>
+          <t>-0,06; 10,12</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 10,97</t>
+          <t>0,35; 10,25</t>
         </is>
       </c>
     </row>
@@ -1293,22 +1293,22 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>33,76%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>20,91%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
           <t>40,69%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>52,49%</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>33,76%</t>
-        </is>
-      </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>60,98%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>37,86%</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-11,62; 132,4</t>
+          <t>-14,01; 121,69</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-19,55; 155,84</t>
+          <t>-25,18; 102,9</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-12,69; 108,96</t>
+          <t>-13,87; 132,68</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-20,72; 102,43</t>
+          <t>-0,41; 162,65</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-3,15; 86,3</t>
+          <t>1,52; 87,15</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-7,33; 97,83</t>
+          <t>2,87; 89,77</t>
         </is>
       </c>
     </row>
